--- a/engine/publish_queue/PHDC/PHDC_Valuation_Model_02092026.xlsx
+++ b/engine/publish_queue/PHDC/PHDC_Valuation_Model_02092026.xlsx
@@ -125,6 +125,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,7 +135,6 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,16 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,6 +760,36 @@
       <c r="F15" s="19" t="n">
         <v>2030</v>
       </c>
+      <c r="G15" s="19" t="n">
+        <v>2031</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>2033</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>2035</v>
+      </c>
+      <c r="L15" s="19" t="n">
+        <v>2036</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>2037</v>
+      </c>
+      <c r="N15" s="19" t="n">
+        <v>2038</v>
+      </c>
+      <c r="O15" s="19" t="n">
+        <v>2039</v>
+      </c>
+      <c r="P15" s="19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -757,20 +797,50 @@
           <t>Trade and notes receivable</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="21" t="n">
         <v>104247.5434</v>
       </c>
-      <c r="C16" s="20" t="n">
-        <v>107203.1736</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>113353.7011</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>124104.2418</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>141477.8814</v>
+      <c r="C16" s="21" t="n">
+        <v>106437.275</v>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>110168.1339</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>115539.0836</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>122675.136</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>131714.4677</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>142759.3565</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>155864.7106</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>171027.5473</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>188178.4383</v>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>207175.9358</v>
+      </c>
+      <c r="M16" s="21" t="n">
+        <v>227804.8743</v>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>250179.4547</v>
+      </c>
+      <c r="O16" s="21" t="n">
+        <v>274421.8718</v>
+      </c>
+      <c r="P16" s="21" t="n">
+        <v>300662.8743</v>
       </c>
     </row>
     <row r="17">
@@ -779,20 +849,50 @@
           <t>Work in progress</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="21" t="n">
         <v>17695.9447</v>
       </c>
-      <c r="C17" s="20" t="n">
-        <v>18197.6608</v>
-      </c>
-      <c r="D17" s="20" t="n">
-        <v>19241.7083</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>21066.6048</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>24015.7675</v>
+      <c r="C17" s="21" t="n">
+        <v>18067.65</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>18700.9606</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>19612.6754</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>20824.0151</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>22358.4351</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>24233.297</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>26457.9213</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>29031.8018</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>31943.1531</v>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>35167.9644</v>
+      </c>
+      <c r="M17" s="21" t="n">
+        <v>38669.7118</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>42467.7805</v>
+      </c>
+      <c r="O17" s="21" t="n">
+        <v>46582.9132</v>
+      </c>
+      <c r="P17" s="21" t="n">
+        <v>51037.3043</v>
       </c>
     </row>
     <row r="18">
@@ -801,20 +901,50 @@
           <t>Other receivables and prepayments</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="21" t="n">
         <v>13013.9604</v>
       </c>
-      <c r="C18" s="20" t="n">
-        <v>13382.9327</v>
-      </c>
-      <c r="D18" s="20" t="n">
-        <v>14150.7467</v>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>15492.813</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <v>17661.6876</v>
+      <c r="C18" s="21" t="n">
+        <v>13287.3202</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>13753.0697</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>14423.5635</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>15314.4075</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>16442.8514</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>17821.6633</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>19457.6976</v>
+      </c>
+      <c r="J18" s="21" t="n">
+        <v>21350.5821</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <v>23491.6495</v>
+      </c>
+      <c r="L18" s="21" t="n">
+        <v>25863.2419</v>
+      </c>
+      <c r="M18" s="21" t="n">
+        <v>28438.4986</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>31231.6762</v>
+      </c>
+      <c r="O18" s="21" t="n">
+        <v>34258.0291</v>
+      </c>
+      <c r="P18" s="21" t="n">
+        <v>37533.8796</v>
       </c>
     </row>
     <row r="19">
@@ -823,20 +953,50 @@
           <t>Advances to suppliers</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="21" t="n">
         <v>9120.6492</v>
       </c>
-      <c r="C19" s="20" t="n">
-        <v>9379.2381</v>
-      </c>
-      <c r="D19" s="20" t="n">
-        <v>9917.349700000001</v>
-      </c>
-      <c r="E19" s="20" t="n">
-        <v>10857.9177</v>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>12377.9427</v>
+      <c r="C19" s="21" t="n">
+        <v>9312.2294</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>9638.643400000001</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>10108.5494</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>10732.8848</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>11523.7387</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>12490.0594</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>13636.6508</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>14963.2519</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>16463.7886</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>18125.8854</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>19930.7175</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>21888.2763</v>
+      </c>
+      <c r="O19" s="21" t="n">
+        <v>24009.2527</v>
+      </c>
+      <c r="P19" s="21" t="n">
+        <v>26305.086</v>
       </c>
     </row>
     <row r="20">
@@ -845,20 +1005,50 @@
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="21" t="n">
         <v>12516.3758</v>
       </c>
-      <c r="C20" s="20" t="n">
-        <v>16975.2575</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>23395.1555</v>
-      </c>
-      <c r="E20" s="20" t="n">
-        <v>32638.5245</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>45947.1273</v>
+      <c r="C20" s="21" t="n">
+        <v>16505.1518</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>21439.866</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>27381.2619</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>34406.0714</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>42599.1067</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>52023.1456</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>62711.8904</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>74663.5105</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <v>87835.391</v>
+      </c>
+      <c r="L20" s="21" t="n">
+        <v>102140.7118</v>
+      </c>
+      <c r="M20" s="21" t="n">
+        <v>117447.405</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>133825.5668</v>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>151350.1999</v>
+      </c>
+      <c r="P20" s="21" t="n">
+        <v>170101.5573</v>
       </c>
     </row>
     <row r="21">
@@ -867,20 +1057,50 @@
           <t>Property and equipment</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="21" t="n">
         <v>4530.8722</v>
       </c>
-      <c r="C21" s="20" t="n">
-        <v>4543.6465</v>
-      </c>
-      <c r="D21" s="20" t="n">
-        <v>4562.0388</v>
-      </c>
-      <c r="E21" s="20" t="n">
-        <v>4588.5201</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>4626.6479</v>
+      <c r="C21" s="21" t="n">
+        <v>4542.2997</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>4556.4371</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>4573.4586</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>4593.584</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>4617.0562</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <v>4644.0551</v>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>4674.6772</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <v>4708.9174</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <v>4746.6534</v>
+      </c>
+      <c r="L21" s="21" t="n">
+        <v>4787.6367</v>
+      </c>
+      <c r="M21" s="21" t="n">
+        <v>4831.4888</v>
+      </c>
+      <c r="N21" s="21" t="n">
+        <v>4878.4106</v>
+      </c>
+      <c r="O21" s="21" t="n">
+        <v>4928.6168</v>
+      </c>
+      <c r="P21" s="21" t="n">
+        <v>4982.3375</v>
       </c>
     </row>
     <row r="22">
@@ -889,19 +1109,49 @@
           <t>Other assets, held at the 2025 level</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="F22" s="20" t="n">
+      <c r="F22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="J22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="K22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="L22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="M22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="N22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="O22" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="P22" s="21" t="n">
         <v>15128.3</v>
       </c>
     </row>
@@ -911,20 +1161,50 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>176253.6456</v>
       </c>
-      <c r="C23" s="21" t="n">
-        <v>184810.2092</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>199749.0001</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>223876.9219</v>
-      </c>
-      <c r="F23" s="21" t="n">
-        <v>261235.3543</v>
+      <c r="C23" s="22" t="n">
+        <v>183280.226</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>193385.4107</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>206766.8924</v>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>223674.3988</v>
+      </c>
+      <c r="G23" s="22" t="n">
+        <v>244383.9558</v>
+      </c>
+      <c r="H23" s="22" t="n">
+        <v>269099.8767</v>
+      </c>
+      <c r="I23" s="22" t="n">
+        <v>297931.8479</v>
+      </c>
+      <c r="J23" s="22" t="n">
+        <v>330873.911</v>
+      </c>
+      <c r="K23" s="22" t="n">
+        <v>367787.3738</v>
+      </c>
+      <c r="L23" s="22" t="n">
+        <v>408389.676</v>
+      </c>
+      <c r="M23" s="22" t="n">
+        <v>452250.996</v>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>499599.4651</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>550679.1836</v>
+      </c>
+      <c r="P23" s="22" t="n">
+        <v>605751.339</v>
       </c>
     </row>
     <row r="24">
@@ -933,20 +1213,50 @@
           <t>Customer advances</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="21" t="n">
         <v>69847.66379999999</v>
       </c>
-      <c r="C24" s="20" t="n">
-        <v>71827.9874</v>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>75948.9476</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>83151.99649999999</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>94792.6367</v>
+      <c r="C24" s="21" t="n">
+        <v>71314.822</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>73814.56230000001</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>77413.1918</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>82194.4708</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>88250.98</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>95651.2472</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>104432.062</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>114591.4258</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>126082.8205</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>138811.4737</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>152633.2206</v>
+      </c>
+      <c r="N24" s="21" t="n">
+        <v>167624.5779</v>
+      </c>
+      <c r="O24" s="21" t="n">
+        <v>183867.4182</v>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>201449.3454</v>
       </c>
     </row>
     <row r="25">
@@ -955,20 +1265,50 @@
           <t>Suppliers</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="21" t="n">
         <v>3834.0928</v>
       </c>
-      <c r="C25" s="20" t="n">
-        <v>3942.7972</v>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>4169.0058</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>4564.3971</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>5203.3776</v>
+      <c r="C25" s="21" t="n">
+        <v>3914.6284</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>4051.8446</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>4249.3814</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>4511.8364</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>4844.2916</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>5250.5086</v>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>5732.5069</v>
+      </c>
+      <c r="J25" s="21" t="n">
+        <v>6290.1769</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <v>6920.965</v>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>7619.6689</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>8378.3752</v>
+      </c>
+      <c r="N25" s="21" t="n">
+        <v>9201.284</v>
+      </c>
+      <c r="O25" s="21" t="n">
+        <v>10092.8894</v>
+      </c>
+      <c r="P25" s="21" t="n">
+        <v>11058.0003</v>
       </c>
     </row>
     <row r="26">
@@ -977,20 +1317,50 @@
           <t>Other creditors</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="21" t="n">
         <v>5158.149</v>
       </c>
-      <c r="C26" s="20" t="n">
-        <v>5304.393</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>5608.72</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <v>6140.6547</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>7000.2991</v>
+      <c r="C26" s="21" t="n">
+        <v>5266.4965</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>5451.0987</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>5716.8523</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>6069.9428</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>6517.2073</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>7063.7063</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>7712.1568</v>
+      </c>
+      <c r="J26" s="21" t="n">
+        <v>8462.411099999999</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>9311.034</v>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>10251.0266</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>11271.7426</v>
+      </c>
+      <c r="N26" s="21" t="n">
+        <v>12378.8327</v>
+      </c>
+      <c r="O26" s="21" t="n">
+        <v>13578.343</v>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>14876.7429</v>
       </c>
     </row>
     <row r="27">
@@ -999,20 +1369,50 @@
           <t>Cheques under collection</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="21" t="n">
         <v>2471.1619</v>
       </c>
-      <c r="C27" s="20" t="n">
-        <v>2541.2244</v>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>2687.0211</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>2941.86</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>3353.6978</v>
+      <c r="C27" s="21" t="n">
+        <v>2523.069</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>2611.5081</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>2738.8251</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>2907.9834</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>3122.2585</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>3384.0748</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>3694.734</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>4054.1652</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>4460.7228</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>4911.0538</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>5400.0576</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>5930.4414</v>
+      </c>
+      <c r="O27" s="21" t="n">
+        <v>6505.1018</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>7127.1382</v>
       </c>
     </row>
     <row r="28">
@@ -1021,19 +1421,49 @@
           <t>Borrowings</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="21" t="n">
         <v>33552.7</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="21" t="n">
         <v>33552.7</v>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="21" t="n">
         <v>33552.7</v>
       </c>
-      <c r="E28" s="20" t="n">
+      <c r="E28" s="21" t="n">
         <v>33552.7</v>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="M28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="P28" s="21" t="n">
         <v>33552.7</v>
       </c>
     </row>
@@ -1043,19 +1473,49 @@
           <t>Other liabilities, held at the 2025 level</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E29" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="F29" s="20" t="n">
+      <c r="F29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="J29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="L29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="N29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="O29" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="P29" s="21" t="n">
         <v>39074.8</v>
       </c>
     </row>
@@ -1065,20 +1525,50 @@
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
+      <c r="B30" s="22" t="n">
         <v>153938.5676</v>
       </c>
-      <c r="C30" s="21" t="n">
-        <v>156243.902</v>
-      </c>
-      <c r="D30" s="21" t="n">
-        <v>161041.1945</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>169426.4083</v>
-      </c>
-      <c r="F30" s="21" t="n">
-        <v>182977.5112</v>
+      <c r="C30" s="22" t="n">
+        <v>155646.5159</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>158556.5137</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>162745.7506</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>168311.7334</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>175362.2373</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>183977.037</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>194198.9597</v>
+      </c>
+      <c r="J30" s="22" t="n">
+        <v>206025.6791</v>
+      </c>
+      <c r="K30" s="22" t="n">
+        <v>219403.0423</v>
+      </c>
+      <c r="L30" s="22" t="n">
+        <v>234220.723</v>
+      </c>
+      <c r="M30" s="22" t="n">
+        <v>250310.896</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>267762.636</v>
+      </c>
+      <c r="O30" s="22" t="n">
+        <v>286671.2524</v>
+      </c>
+      <c r="P30" s="22" t="n">
+        <v>307138.7268</v>
       </c>
     </row>
     <row r="31">
@@ -1087,20 +1577,50 @@
           <t>Shareholders' funds</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="21" t="n">
         <v>22315.078</v>
       </c>
-      <c r="C31" s="20" t="n">
-        <v>28566.3072</v>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>38707.8056</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>54450.5136</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>78257.8432</v>
+      <c r="C31" s="21" t="n">
+        <v>27633.7101</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>34828.8971</v>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>44021.1419</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>55362.6654</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>69021.7185</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>85122.8397</v>
+      </c>
+      <c r="I31" s="21" t="n">
+        <v>103732.8882</v>
+      </c>
+      <c r="J31" s="21" t="n">
+        <v>124848.2319</v>
+      </c>
+      <c r="K31" s="21" t="n">
+        <v>148384.3315</v>
+      </c>
+      <c r="L31" s="21" t="n">
+        <v>174168.953</v>
+      </c>
+      <c r="M31" s="21" t="n">
+        <v>201940.1</v>
+      </c>
+      <c r="N31" s="21" t="n">
+        <v>231836.8291</v>
+      </c>
+      <c r="O31" s="21" t="n">
+        <v>264007.9311</v>
+      </c>
+      <c r="P31" s="21" t="n">
+        <v>298612.6121</v>
       </c>
     </row>
     <row r="32">
@@ -1109,20 +1629,50 @@
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="22" t="n">
         <v>176253.6456</v>
       </c>
-      <c r="C32" s="21" t="n">
-        <v>184810.2092</v>
-      </c>
-      <c r="D32" s="21" t="n">
-        <v>199749.0001</v>
-      </c>
-      <c r="E32" s="21" t="n">
-        <v>223876.9219</v>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>261235.3543</v>
+      <c r="C32" s="22" t="n">
+        <v>183280.226</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>193385.4107</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>206766.8924</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>223674.3988</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>244383.9558</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>269099.8767</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>297931.8479</v>
+      </c>
+      <c r="J32" s="22" t="n">
+        <v>330873.911</v>
+      </c>
+      <c r="K32" s="22" t="n">
+        <v>367787.3738</v>
+      </c>
+      <c r="L32" s="22" t="n">
+        <v>408389.676</v>
+      </c>
+      <c r="M32" s="22" t="n">
+        <v>452250.996</v>
+      </c>
+      <c r="N32" s="22" t="n">
+        <v>499599.4651</v>
+      </c>
+      <c r="O32" s="22" t="n">
+        <v>550679.1836</v>
+      </c>
+      <c r="P32" s="22" t="n">
+        <v>605751.339</v>
       </c>
     </row>
     <row r="33">
@@ -1131,19 +1681,49 @@
           <t>Check: assets less liabilities and equity</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="27" t="n">
         <v>-0</v>
       </c>
-      <c r="D33" s="26" t="n">
+      <c r="E33" s="27" t="n">
         <v>-0</v>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="F33" s="27" t="n">
         <v>-0</v>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="G33" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J33" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1153,20 +1733,50 @@
           <t>Collection period, days</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
+      <c r="B34" s="21" t="n">
         <v>947.754</v>
       </c>
-      <c r="C34" s="20" t="n">
-        <v>676.9167</v>
-      </c>
-      <c r="D34" s="20" t="n">
-        <v>497.1199</v>
-      </c>
-      <c r="E34" s="20" t="n">
-        <v>378.0158</v>
-      </c>
-      <c r="F34" s="20" t="n">
-        <v>299.302</v>
+      <c r="C34" s="21" t="n">
+        <v>751.2901000000001</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>628.5612</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>547.5124</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>491.6721</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>452.6288</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>426.502</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>410.5581</v>
+      </c>
+      <c r="J34" s="21" t="n">
+        <v>402.8959</v>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>402.2311</v>
+      </c>
+      <c r="L34" s="21" t="n">
+        <v>407.7512</v>
+      </c>
+      <c r="M34" s="21" t="n">
+        <v>419.0204</v>
+      </c>
+      <c r="N34" s="21" t="n">
+        <v>430.0709</v>
+      </c>
+      <c r="O34" s="21" t="n">
+        <v>440.883</v>
+      </c>
+      <c r="P34" s="21" t="n">
+        <v>451.4406</v>
       </c>
     </row>
     <row r="35">
@@ -1175,20 +1785,50 @@
           <t>Work in progress, days of cost</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="21" t="n">
         <v>260.841</v>
       </c>
-      <c r="C35" s="20" t="n">
-        <v>186.3011</v>
-      </c>
-      <c r="D35" s="20" t="n">
-        <v>136.8174</v>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>104.0376</v>
-      </c>
-      <c r="F35" s="20" t="n">
-        <v>82.374</v>
+      <c r="C35" s="21" t="n">
+        <v>206.7702</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>172.9927</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>150.6865</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>135.3181</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>124.5726</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <v>117.382</v>
+      </c>
+      <c r="I35" s="21" t="n">
+        <v>112.9939</v>
+      </c>
+      <c r="J35" s="21" t="n">
+        <v>110.8851</v>
+      </c>
+      <c r="K35" s="21" t="n">
+        <v>110.7021</v>
+      </c>
+      <c r="L35" s="21" t="n">
+        <v>112.2214</v>
+      </c>
+      <c r="M35" s="21" t="n">
+        <v>115.3229</v>
+      </c>
+      <c r="N35" s="21" t="n">
+        <v>118.3642</v>
+      </c>
+      <c r="O35" s="21" t="n">
+        <v>121.3399</v>
+      </c>
+      <c r="P35" s="21" t="n">
+        <v>124.2456</v>
       </c>
     </row>
     <row r="36">
@@ -1197,20 +1837,50 @@
           <t>Suppliers, days of cost</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
+      <c r="B36" s="21" t="n">
         <v>56.5151</v>
       </c>
-      <c r="C36" s="20" t="n">
-        <v>40.3649</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>29.6436</v>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>22.5413</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>17.8476</v>
+      <c r="C36" s="21" t="n">
+        <v>44.7999</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>37.4815</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>32.6485</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>29.3187</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>26.9905</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>25.4326</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>24.4818</v>
+      </c>
+      <c r="J36" s="21" t="n">
+        <v>24.0249</v>
+      </c>
+      <c r="K36" s="21" t="n">
+        <v>23.9853</v>
+      </c>
+      <c r="L36" s="21" t="n">
+        <v>24.3144</v>
+      </c>
+      <c r="M36" s="21" t="n">
+        <v>24.9864</v>
+      </c>
+      <c r="N36" s="21" t="n">
+        <v>25.6454</v>
+      </c>
+      <c r="O36" s="21" t="n">
+        <v>26.2901</v>
+      </c>
+      <c r="P36" s="21" t="n">
+        <v>26.9197</v>
       </c>
     </row>
     <row r="37">
@@ -1220,19 +1890,49 @@
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>0.1925</v>
+        <v>0.1981</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>0.1495</v>
+        <v>0.1599</v>
       </c>
       <c r="D37" s="17" t="n">
-        <v>0.1232</v>
+        <v>0.1366</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>0.1078</v>
+        <v>0.1222</v>
       </c>
       <c r="F37" s="17" t="n">
-        <v>0.1005</v>
+        <v>0.1134</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>0.1063</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>0.1215</v>
       </c>
     </row>
     <row r="38">
@@ -1241,20 +1941,50 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
+      <c r="B38" s="21" t="n">
         <v>62767.03</v>
       </c>
-      <c r="C38" s="20" t="n">
-        <v>64546.6032</v>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>68249.8113</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>74722.66899999999</v>
-      </c>
-      <c r="F38" s="20" t="n">
-        <v>85183.268</v>
+      <c r="C38" s="21" t="n">
+        <v>64085.4587</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>66331.79399999999</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>69565.6214</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>73862.2101</v>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>79304.7556</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>85954.8391</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>93845.5206</v>
+      </c>
+      <c r="J38" s="21" t="n">
+        <v>102975.004</v>
+      </c>
+      <c r="K38" s="21" t="n">
+        <v>113301.4871</v>
+      </c>
+      <c r="L38" s="21" t="n">
+        <v>124739.8046</v>
+      </c>
+      <c r="M38" s="21" t="n">
+        <v>137160.4062</v>
+      </c>
+      <c r="N38" s="21" t="n">
+        <v>150632.0517</v>
+      </c>
+      <c r="O38" s="21" t="n">
+        <v>165228.3144</v>
+      </c>
+      <c r="P38" s="21" t="n">
+        <v>181027.9173</v>
       </c>
     </row>
     <row r="39">
@@ -1267,16 +1997,46 @@
         <v>1.5634</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>1.1166</v>
+        <v>1.2393</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.82</v>
+        <v>1.0369</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.6236</v>
+        <v>0.9032</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.4937</v>
+        <v>0.8111</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0.7466</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="L39" s="7" t="n">
+        <v>0.6726</v>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>0.6912</v>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>0.7094</v>
+      </c>
+      <c r="O39" s="7" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="P39" s="7" t="n">
+        <v>0.7447</v>
       </c>
     </row>
     <row r="41">
@@ -1307,6 +2067,36 @@
       <c r="F42" s="19" t="n">
         <v>2030</v>
       </c>
+      <c r="G42" s="19" t="n">
+        <v>2031</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>2033</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>2035</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>2036</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>2037</v>
+      </c>
+      <c r="N42" s="19" t="n">
+        <v>2038</v>
+      </c>
+      <c r="O42" s="19" t="n">
+        <v>2039</v>
+      </c>
+      <c r="P42" s="19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -1314,20 +2104,50 @@
           <t>Trade and notes receivable</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n">
+      <c r="B43" s="21" t="n">
         <v>114897.099</v>
       </c>
-      <c r="C43" s="20" t="n">
-        <v>165428.8431</v>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>238184.4484</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>342937.9687</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>493762.0874</v>
+      <c r="C43" s="21" t="n">
+        <v>147987.4635</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>183082.6905</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>220431.5593</v>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>260627.2542</v>
+      </c>
+      <c r="G43" s="21" t="n">
+        <v>303969.5666</v>
+      </c>
+      <c r="H43" s="21" t="n">
+        <v>349640.9939</v>
+      </c>
+      <c r="I43" s="21" t="n">
+        <v>396562.8153</v>
+      </c>
+      <c r="J43" s="21" t="n">
+        <v>443416.712</v>
+      </c>
+      <c r="K43" s="21" t="n">
+        <v>488689.5582</v>
+      </c>
+      <c r="L43" s="21" t="n">
+        <v>530741.2947</v>
+      </c>
+      <c r="M43" s="21" t="n">
+        <v>567893.1854</v>
+      </c>
+      <c r="N43" s="21" t="n">
+        <v>607645.7083000001</v>
+      </c>
+      <c r="O43" s="21" t="n">
+        <v>650180.9079</v>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>695693.5715</v>
       </c>
     </row>
     <row r="44">
@@ -1336,20 +2156,50 @@
           <t>Work in progress</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="21" t="n">
         <v>19503.699</v>
       </c>
-      <c r="C44" s="20" t="n">
-        <v>28081.4258</v>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>40431.6369</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>58213.4708</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>83815.7553</v>
+      <c r="C44" s="21" t="n">
+        <v>25120.7643</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>31078.1536</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>37418.0969</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>44241.2869</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>51598.6129</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>59351.3045</v>
+      </c>
+      <c r="I44" s="21" t="n">
+        <v>67316.24950000001</v>
+      </c>
+      <c r="J44" s="21" t="n">
+        <v>75269.66439999999</v>
+      </c>
+      <c r="K44" s="21" t="n">
+        <v>82954.6971</v>
+      </c>
+      <c r="L44" s="21" t="n">
+        <v>90092.9488</v>
+      </c>
+      <c r="M44" s="21" t="n">
+        <v>96399.4552</v>
+      </c>
+      <c r="N44" s="21" t="n">
+        <v>103147.4171</v>
+      </c>
+      <c r="O44" s="21" t="n">
+        <v>110367.7363</v>
+      </c>
+      <c r="P44" s="21" t="n">
+        <v>118093.4778</v>
       </c>
     </row>
     <row r="45">
@@ -1358,20 +2208,50 @@
           <t>Other receivables and prepayments</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
+      <c r="B45" s="21" t="n">
         <v>14343.42</v>
       </c>
-      <c r="C45" s="20" t="n">
-        <v>20651.6561</v>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>29734.2545</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>42811.3796</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>61639.8243</v>
+      <c r="C45" s="21" t="n">
+        <v>18474.325</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>22855.5111</v>
+      </c>
+      <c r="E45" s="21" t="n">
+        <v>27518.0354</v>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>32535.9491</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <v>37946.6775</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <v>43648.1658</v>
+      </c>
+      <c r="I45" s="21" t="n">
+        <v>49505.7496</v>
+      </c>
+      <c r="J45" s="21" t="n">
+        <v>55354.854</v>
+      </c>
+      <c r="K45" s="21" t="n">
+        <v>61006.5845</v>
+      </c>
+      <c r="L45" s="21" t="n">
+        <v>66256.20110000001</v>
+      </c>
+      <c r="M45" s="21" t="n">
+        <v>70894.1352</v>
+      </c>
+      <c r="N45" s="21" t="n">
+        <v>75856.72470000001</v>
+      </c>
+      <c r="O45" s="21" t="n">
+        <v>81166.6954</v>
+      </c>
+      <c r="P45" s="21" t="n">
+        <v>86848.36410000001</v>
       </c>
     </row>
     <row r="46">
@@ -1380,20 +2260,50 @@
           <t>Advances to suppliers</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n">
+      <c r="B46" s="21" t="n">
         <v>10052.382</v>
       </c>
-      <c r="C46" s="20" t="n">
-        <v>14473.4196</v>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>20838.8295</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>30003.7468</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>43199.3946</v>
+      <c r="C46" s="21" t="n">
+        <v>12947.468</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>16017.9601</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>19285.6239</v>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>22802.3574</v>
+      </c>
+      <c r="G46" s="21" t="n">
+        <v>26594.3895</v>
+      </c>
+      <c r="H46" s="21" t="n">
+        <v>30590.1965</v>
+      </c>
+      <c r="I46" s="21" t="n">
+        <v>34695.4009</v>
+      </c>
+      <c r="J46" s="21" t="n">
+        <v>38794.6625</v>
+      </c>
+      <c r="K46" s="21" t="n">
+        <v>42755.5975</v>
+      </c>
+      <c r="L46" s="21" t="n">
+        <v>46434.7167</v>
+      </c>
+      <c r="M46" s="21" t="n">
+        <v>49685.1468</v>
+      </c>
+      <c r="N46" s="21" t="n">
+        <v>53163.1071</v>
+      </c>
+      <c r="O46" s="21" t="n">
+        <v>56884.5246</v>
+      </c>
+      <c r="P46" s="21" t="n">
+        <v>60866.4413</v>
       </c>
     </row>
     <row r="47">
@@ -1402,20 +2312,50 @@
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n">
+      <c r="B47" s="21" t="n">
         <v>6104.3208</v>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C47" s="21" t="n">
         <v>2354.875</v>
       </c>
-      <c r="D47" s="20" t="n">
+      <c r="D47" s="21" t="n">
         <v>2354.875</v>
       </c>
-      <c r="E47" s="20" t="n">
+      <c r="E47" s="21" t="n">
         <v>2354.875</v>
       </c>
-      <c r="F47" s="20" t="n">
+      <c r="F47" s="21" t="n">
         <v>2354.875</v>
+      </c>
+      <c r="G47" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="H47" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="I47" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="J47" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="K47" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="L47" s="21" t="n">
+        <v>2779.3305</v>
+      </c>
+      <c r="M47" s="21" t="n">
+        <v>8137.6202</v>
+      </c>
+      <c r="N47" s="21" t="n">
+        <v>14052.592</v>
+      </c>
+      <c r="O47" s="21" t="n">
+        <v>20563.2138</v>
+      </c>
+      <c r="P47" s="21" t="n">
+        <v>27711.1809</v>
       </c>
     </row>
     <row r="48">
@@ -1424,20 +2364,50 @@
           <t>Property and equipment</t>
         </is>
       </c>
-      <c r="B48" s="20" t="n">
+      <c r="B48" s="21" t="n">
         <v>4530.8722</v>
       </c>
-      <c r="C48" s="20" t="n">
-        <v>4543.6465</v>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4562.0388</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4588.5201</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>4626.6479</v>
+      <c r="C48" s="21" t="n">
+        <v>4542.2997</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>4556.4371</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>4573.4586</v>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>4593.584</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>4617.0562</v>
+      </c>
+      <c r="H48" s="21" t="n">
+        <v>4644.0551</v>
+      </c>
+      <c r="I48" s="21" t="n">
+        <v>4674.6772</v>
+      </c>
+      <c r="J48" s="21" t="n">
+        <v>4708.9174</v>
+      </c>
+      <c r="K48" s="21" t="n">
+        <v>4746.6534</v>
+      </c>
+      <c r="L48" s="21" t="n">
+        <v>4787.6367</v>
+      </c>
+      <c r="M48" s="21" t="n">
+        <v>4831.4888</v>
+      </c>
+      <c r="N48" s="21" t="n">
+        <v>4878.4106</v>
+      </c>
+      <c r="O48" s="21" t="n">
+        <v>4928.6168</v>
+      </c>
+      <c r="P48" s="21" t="n">
+        <v>4982.3375</v>
       </c>
     </row>
     <row r="49">
@@ -1446,19 +2416,49 @@
           <t>Other assets, held at the 2025 level</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n">
+      <c r="B49" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="C49" s="20" t="n">
+      <c r="C49" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="D49" s="20" t="n">
+      <c r="D49" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="E49" s="20" t="n">
+      <c r="E49" s="21" t="n">
         <v>15128.3</v>
       </c>
-      <c r="F49" s="20" t="n">
+      <c r="F49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="G49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="H49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="I49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="J49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="K49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="L49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="M49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="N49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="O49" s="21" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="P49" s="21" t="n">
         <v>15128.3</v>
       </c>
     </row>
@@ -1468,20 +2468,50 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n">
+      <c r="B50" s="22" t="n">
         <v>184560.093</v>
       </c>
-      <c r="C50" s="21" t="n">
-        <v>250662.1661</v>
-      </c>
-      <c r="D50" s="21" t="n">
-        <v>351234.3831</v>
-      </c>
-      <c r="E50" s="21" t="n">
-        <v>496038.261</v>
-      </c>
-      <c r="F50" s="21" t="n">
-        <v>704526.8845</v>
+      <c r="C50" s="22" t="n">
+        <v>226555.4955</v>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>275073.9273</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>326709.9491</v>
+      </c>
+      <c r="F50" s="22" t="n">
+        <v>382283.6066</v>
+      </c>
+      <c r="G50" s="22" t="n">
+        <v>442209.4775</v>
+      </c>
+      <c r="H50" s="22" t="n">
+        <v>505357.8907</v>
+      </c>
+      <c r="I50" s="22" t="n">
+        <v>570238.0675</v>
+      </c>
+      <c r="J50" s="22" t="n">
+        <v>635027.9851</v>
+      </c>
+      <c r="K50" s="22" t="n">
+        <v>697636.2659</v>
+      </c>
+      <c r="L50" s="22" t="n">
+        <v>756220.4286</v>
+      </c>
+      <c r="M50" s="22" t="n">
+        <v>812969.3316</v>
+      </c>
+      <c r="N50" s="22" t="n">
+        <v>873872.2598</v>
+      </c>
+      <c r="O50" s="22" t="n">
+        <v>939219.9948</v>
+      </c>
+      <c r="P50" s="22" t="n">
+        <v>1009323.6732</v>
       </c>
     </row>
     <row r="51">
@@ -1490,20 +2520,50 @@
           <t>Customer advances</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n">
+      <c r="B51" s="21" t="n">
         <v>76983.05100000001</v>
       </c>
-      <c r="C51" s="20" t="n">
-        <v>110840.1968</v>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>159587.7154</v>
-      </c>
-      <c r="E51" s="20" t="n">
-        <v>229774.3926</v>
-      </c>
-      <c r="F51" s="20" t="n">
-        <v>330829.1705</v>
+      <c r="C51" s="21" t="n">
+        <v>99154.1697</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>122668.581</v>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>147692.9716</v>
+      </c>
+      <c r="F51" s="21" t="n">
+        <v>174624.7849</v>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>203664.8867</v>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>234265.5359</v>
+      </c>
+      <c r="I51" s="21" t="n">
+        <v>265703.9708</v>
+      </c>
+      <c r="J51" s="21" t="n">
+        <v>297096.8949</v>
+      </c>
+      <c r="K51" s="21" t="n">
+        <v>327430.4879</v>
+      </c>
+      <c r="L51" s="21" t="n">
+        <v>355605.8814</v>
+      </c>
+      <c r="M51" s="21" t="n">
+        <v>380498.2931</v>
+      </c>
+      <c r="N51" s="21" t="n">
+        <v>407133.1736</v>
+      </c>
+      <c r="O51" s="21" t="n">
+        <v>435632.4958</v>
+      </c>
+      <c r="P51" s="21" t="n">
+        <v>466126.7705</v>
       </c>
     </row>
     <row r="52">
@@ -1512,20 +2572,50 @@
           <t>Suppliers</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n">
+      <c r="B52" s="21" t="n">
         <v>4225.77</v>
       </c>
-      <c r="C52" s="20" t="n">
-        <v>6084.2636</v>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>8760.122799999999</v>
-      </c>
-      <c r="E52" s="20" t="n">
-        <v>12612.8248</v>
-      </c>
-      <c r="F52" s="20" t="n">
-        <v>18159.9452</v>
+      <c r="C52" s="21" t="n">
+        <v>5442.7918</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>6733.5498</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>8107.194</v>
+      </c>
+      <c r="F52" s="21" t="n">
+        <v>9585.540800000001</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>11179.6163</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>12859.3536</v>
+      </c>
+      <c r="I52" s="21" t="n">
+        <v>14585.0788</v>
+      </c>
+      <c r="J52" s="21" t="n">
+        <v>16308.3059</v>
+      </c>
+      <c r="K52" s="21" t="n">
+        <v>17973.3839</v>
+      </c>
+      <c r="L52" s="21" t="n">
+        <v>19519.9936</v>
+      </c>
+      <c r="M52" s="21" t="n">
+        <v>20886.3932</v>
+      </c>
+      <c r="N52" s="21" t="n">
+        <v>22348.4407</v>
+      </c>
+      <c r="O52" s="21" t="n">
+        <v>23912.8316</v>
+      </c>
+      <c r="P52" s="21" t="n">
+        <v>25586.7298</v>
       </c>
     </row>
     <row r="53">
@@ -1534,20 +2624,50 @@
           <t>Other creditors</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n">
+      <c r="B53" s="21" t="n">
         <v>5685.087</v>
       </c>
-      <c r="C53" s="20" t="n">
-        <v>8185.3883</v>
-      </c>
-      <c r="D53" s="20" t="n">
-        <v>11785.322</v>
-      </c>
-      <c r="E53" s="20" t="n">
-        <v>16968.5066</v>
-      </c>
-      <c r="F53" s="20" t="n">
-        <v>24431.2559</v>
+      <c r="C53" s="21" t="n">
+        <v>7322.3921</v>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>9058.897300000001</v>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>10906.9124</v>
+      </c>
+      <c r="F53" s="21" t="n">
+        <v>12895.7879</v>
+      </c>
+      <c r="G53" s="21" t="n">
+        <v>15040.3574</v>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>17300.1711</v>
+      </c>
+      <c r="I53" s="21" t="n">
+        <v>19621.854</v>
+      </c>
+      <c r="J53" s="21" t="n">
+        <v>21940.1761</v>
+      </c>
+      <c r="K53" s="21" t="n">
+        <v>24180.2681</v>
+      </c>
+      <c r="L53" s="21" t="n">
+        <v>26260.9801</v>
+      </c>
+      <c r="M53" s="21" t="n">
+        <v>28099.2488</v>
+      </c>
+      <c r="N53" s="21" t="n">
+        <v>30066.1962</v>
+      </c>
+      <c r="O53" s="21" t="n">
+        <v>32170.8299</v>
+      </c>
+      <c r="P53" s="21" t="n">
+        <v>34422.788</v>
       </c>
     </row>
     <row r="54">
@@ -1556,20 +2676,50 @@
           <t>Cheques under collection</t>
         </is>
       </c>
-      <c r="B54" s="20" t="n">
+      <c r="B54" s="21" t="n">
         <v>2723.607</v>
       </c>
-      <c r="C54" s="20" t="n">
-        <v>3921.4494</v>
-      </c>
-      <c r="D54" s="20" t="n">
-        <v>5646.1028</v>
-      </c>
-      <c r="E54" s="20" t="n">
-        <v>8129.2588</v>
-      </c>
-      <c r="F54" s="20" t="n">
-        <v>11704.5068</v>
+      <c r="C54" s="21" t="n">
+        <v>3508.0058</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>4339.9294</v>
+      </c>
+      <c r="E54" s="21" t="n">
+        <v>5225.275</v>
+      </c>
+      <c r="F54" s="21" t="n">
+        <v>6178.1039</v>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>7205.5226</v>
+      </c>
+      <c r="H54" s="21" t="n">
+        <v>8288.1523</v>
+      </c>
+      <c r="I54" s="21" t="n">
+        <v>9400.422399999999</v>
+      </c>
+      <c r="J54" s="21" t="n">
+        <v>10511.0823</v>
+      </c>
+      <c r="K54" s="21" t="n">
+        <v>11584.2638</v>
+      </c>
+      <c r="L54" s="21" t="n">
+        <v>12581.0897</v>
+      </c>
+      <c r="M54" s="21" t="n">
+        <v>13461.7659</v>
+      </c>
+      <c r="N54" s="21" t="n">
+        <v>14404.0896</v>
+      </c>
+      <c r="O54" s="21" t="n">
+        <v>15412.3758</v>
+      </c>
+      <c r="P54" s="21" t="n">
+        <v>16491.2421</v>
       </c>
     </row>
     <row r="55">
@@ -1578,20 +2728,50 @@
           <t>Borrowings</t>
         </is>
       </c>
-      <c r="B55" s="20" t="n">
+      <c r="B55" s="21" t="n">
         <v>33552.7</v>
       </c>
-      <c r="C55" s="20" t="n">
-        <v>53989.7609</v>
-      </c>
-      <c r="D55" s="20" t="n">
-        <v>87672.5145</v>
-      </c>
-      <c r="E55" s="20" t="n">
-        <v>135027.9646</v>
-      </c>
-      <c r="F55" s="20" t="n">
-        <v>202069.363</v>
+      <c r="C55" s="21" t="n">
+        <v>44419.626</v>
+      </c>
+      <c r="D55" s="21" t="n">
+        <v>58369.2727</v>
+      </c>
+      <c r="E55" s="21" t="n">
+        <v>71681.65429999999</v>
+      </c>
+      <c r="F55" s="21" t="n">
+        <v>84561.9237</v>
+      </c>
+      <c r="G55" s="21" t="n">
+        <v>97022.5762</v>
+      </c>
+      <c r="H55" s="21" t="n">
+        <v>108447.0381</v>
+      </c>
+      <c r="I55" s="21" t="n">
+        <v>118119.0533</v>
+      </c>
+      <c r="J55" s="21" t="n">
+        <v>125248.494</v>
+      </c>
+      <c r="K55" s="21" t="n">
+        <v>129008.7307</v>
+      </c>
+      <c r="L55" s="21" t="n">
+        <v>129008.7307</v>
+      </c>
+      <c r="M55" s="21" t="n">
+        <v>129008.7307</v>
+      </c>
+      <c r="N55" s="21" t="n">
+        <v>129008.7307</v>
+      </c>
+      <c r="O55" s="21" t="n">
+        <v>129008.7307</v>
+      </c>
+      <c r="P55" s="21" t="n">
+        <v>129008.7307</v>
       </c>
     </row>
     <row r="56">
@@ -1600,19 +2780,49 @@
           <t>Other liabilities, held at the 2025 level</t>
         </is>
       </c>
-      <c r="B56" s="20" t="n">
+      <c r="B56" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="C56" s="20" t="n">
+      <c r="C56" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="D56" s="20" t="n">
+      <c r="D56" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="E56" s="20" t="n">
+      <c r="E56" s="21" t="n">
         <v>39074.8</v>
       </c>
-      <c r="F56" s="20" t="n">
+      <c r="F56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="G56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="H56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="I56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="J56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="K56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="L56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="M56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="N56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="O56" s="21" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="P56" s="21" t="n">
         <v>39074.8</v>
       </c>
     </row>
@@ -1622,20 +2832,50 @@
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B57" s="21" t="n">
+      <c r="B57" s="22" t="n">
         <v>162245.015</v>
       </c>
-      <c r="C57" s="21" t="n">
-        <v>222095.859</v>
-      </c>
-      <c r="D57" s="21" t="n">
-        <v>312526.5775</v>
-      </c>
-      <c r="E57" s="21" t="n">
-        <v>441587.7475</v>
-      </c>
-      <c r="F57" s="21" t="n">
-        <v>626269.0413</v>
+      <c r="C57" s="22" t="n">
+        <v>198921.7853</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>240245.0303</v>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>282688.8073</v>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>326920.9412</v>
+      </c>
+      <c r="G57" s="22" t="n">
+        <v>373187.7591</v>
+      </c>
+      <c r="H57" s="22" t="n">
+        <v>420235.051</v>
+      </c>
+      <c r="I57" s="22" t="n">
+        <v>466505.1793</v>
+      </c>
+      <c r="J57" s="22" t="n">
+        <v>510179.7532</v>
+      </c>
+      <c r="K57" s="22" t="n">
+        <v>549251.9344</v>
+      </c>
+      <c r="L57" s="22" t="n">
+        <v>582051.4754999999</v>
+      </c>
+      <c r="M57" s="22" t="n">
+        <v>611029.2316000001</v>
+      </c>
+      <c r="N57" s="22" t="n">
+        <v>642035.4307</v>
+      </c>
+      <c r="O57" s="22" t="n">
+        <v>675212.0637000001</v>
+      </c>
+      <c r="P57" s="22" t="n">
+        <v>710711.061</v>
       </c>
     </row>
     <row r="58">
@@ -1644,20 +2884,50 @@
           <t>Shareholders' funds</t>
         </is>
       </c>
-      <c r="B58" s="20" t="n">
+      <c r="B58" s="21" t="n">
         <v>22315.078</v>
       </c>
-      <c r="C58" s="20" t="n">
-        <v>28566.3072</v>
-      </c>
-      <c r="D58" s="20" t="n">
-        <v>38707.8056</v>
-      </c>
-      <c r="E58" s="20" t="n">
-        <v>54450.5136</v>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>78257.8432</v>
+      <c r="C58" s="21" t="n">
+        <v>27633.7101</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>34828.8971</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>44021.1419</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>55362.6654</v>
+      </c>
+      <c r="G58" s="21" t="n">
+        <v>69021.7185</v>
+      </c>
+      <c r="H58" s="21" t="n">
+        <v>85122.8397</v>
+      </c>
+      <c r="I58" s="21" t="n">
+        <v>103732.8882</v>
+      </c>
+      <c r="J58" s="21" t="n">
+        <v>124848.2319</v>
+      </c>
+      <c r="K58" s="21" t="n">
+        <v>148384.3315</v>
+      </c>
+      <c r="L58" s="21" t="n">
+        <v>174168.953</v>
+      </c>
+      <c r="M58" s="21" t="n">
+        <v>201940.1</v>
+      </c>
+      <c r="N58" s="21" t="n">
+        <v>231836.8291</v>
+      </c>
+      <c r="O58" s="21" t="n">
+        <v>264007.9311</v>
+      </c>
+      <c r="P58" s="21" t="n">
+        <v>298612.6121</v>
       </c>
     </row>
     <row r="59">
@@ -1666,20 +2936,50 @@
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="B59" s="21" t="n">
+      <c r="B59" s="22" t="n">
         <v>184560.093</v>
       </c>
-      <c r="C59" s="21" t="n">
-        <v>250662.1661</v>
-      </c>
-      <c r="D59" s="21" t="n">
-        <v>351234.3831</v>
-      </c>
-      <c r="E59" s="21" t="n">
-        <v>496038.261</v>
-      </c>
-      <c r="F59" s="21" t="n">
-        <v>704526.8845</v>
+      <c r="C59" s="22" t="n">
+        <v>226555.4955</v>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>275073.9273</v>
+      </c>
+      <c r="E59" s="22" t="n">
+        <v>326709.9491</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>382283.6066</v>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>442209.4775</v>
+      </c>
+      <c r="H59" s="22" t="n">
+        <v>505357.8907</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>570238.0675</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <v>635027.9851</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <v>697636.2659</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <v>756220.4286</v>
+      </c>
+      <c r="M59" s="22" t="n">
+        <v>812969.3316</v>
+      </c>
+      <c r="N59" s="22" t="n">
+        <v>873872.2598</v>
+      </c>
+      <c r="O59" s="22" t="n">
+        <v>939219.9948</v>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>1009323.6732</v>
       </c>
     </row>
     <row r="60">
@@ -1688,19 +2988,49 @@
           <t>Check: assets less liabilities and equity</t>
         </is>
       </c>
-      <c r="B60" s="26" t="n">
+      <c r="B60" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C60" s="26" t="n">
+      <c r="C60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="27" t="n">
         <v>-0</v>
       </c>
-      <c r="D60" s="26" t="n">
+      <c r="E60" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="26" t="n">
+      <c r="F60" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H60" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I60" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="26" t="n">
+      <c r="J60" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O60" s="27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P60" s="27" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1710,19 +3040,49 @@
           <t>Collection period, days</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n">
+      <c r="B61" s="21" t="n">
         <v>1044.5731</v>
       </c>
-      <c r="C61" s="20" t="n">
+      <c r="C61" s="21" t="n">
         <v>1044.5731</v>
       </c>
-      <c r="D61" s="20" t="n">
+      <c r="D61" s="21" t="n">
         <v>1044.5731</v>
       </c>
-      <c r="E61" s="20" t="n">
+      <c r="E61" s="21" t="n">
         <v>1044.5731</v>
       </c>
-      <c r="F61" s="20" t="n">
+      <c r="F61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="H61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="I61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="J61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="K61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="L61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="M61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="N61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="O61" s="21" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="P61" s="21" t="n">
         <v>1044.5731</v>
       </c>
     </row>
@@ -1732,19 +3092,49 @@
           <t>Work in progress, days of cost</t>
         </is>
       </c>
-      <c r="B62" s="20" t="n">
+      <c r="B62" s="21" t="n">
         <v>287.4876</v>
       </c>
-      <c r="C62" s="20" t="n">
+      <c r="C62" s="21" t="n">
         <v>287.4876</v>
       </c>
-      <c r="D62" s="20" t="n">
+      <c r="D62" s="21" t="n">
         <v>287.4876</v>
       </c>
-      <c r="E62" s="20" t="n">
+      <c r="E62" s="21" t="n">
         <v>287.4876</v>
       </c>
-      <c r="F62" s="20" t="n">
+      <c r="F62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="G62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="H62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="I62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="J62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="K62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="L62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="M62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="N62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="O62" s="21" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="P62" s="21" t="n">
         <v>287.4876</v>
       </c>
     </row>
@@ -1754,19 +3144,49 @@
           <t>Suppliers, days of cost</t>
         </is>
       </c>
-      <c r="B63" s="20" t="n">
+      <c r="B63" s="21" t="n">
         <v>62.2885</v>
       </c>
-      <c r="C63" s="20" t="n">
+      <c r="C63" s="21" t="n">
         <v>62.2885</v>
       </c>
-      <c r="D63" s="20" t="n">
+      <c r="D63" s="21" t="n">
         <v>62.2885</v>
       </c>
-      <c r="E63" s="20" t="n">
+      <c r="E63" s="21" t="n">
         <v>62.2885</v>
       </c>
-      <c r="F63" s="20" t="n">
+      <c r="F63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="G63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="H63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="I63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="J63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="K63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="L63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="M63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="N63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="O63" s="21" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="P63" s="21" t="n">
         <v>62.2885</v>
       </c>
     </row>
@@ -1777,19 +3197,49 @@
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>0.2122</v>
+        <v>0.2184</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>0.2308</v>
+        <v>0.2223</v>
       </c>
       <c r="D64" s="17" t="n">
-        <v>0.2588</v>
+        <v>0.2269</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>0.2978</v>
+        <v>0.2331</v>
       </c>
       <c r="F64" s="17" t="n">
-        <v>0.3509</v>
+        <v>0.2409</v>
+      </c>
+      <c r="G64" s="17" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="H64" s="17" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="I64" s="17" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="J64" s="17" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="K64" s="17" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="L64" s="17" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="M64" s="17" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="N64" s="17" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="O64" s="17" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="P64" s="17" t="n">
+        <v>0.2811</v>
       </c>
     </row>
     <row r="65">
@@ -1798,20 +3248,50 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B65" s="20" t="n">
+      <c r="B65" s="21" t="n">
         <v>69179.08500000001</v>
       </c>
-      <c r="C65" s="20" t="n">
-        <v>99604.0466</v>
-      </c>
-      <c r="D65" s="20" t="n">
-        <v>143409.9063</v>
-      </c>
-      <c r="E65" s="20" t="n">
-        <v>206481.583</v>
-      </c>
-      <c r="F65" s="20" t="n">
-        <v>297292.1833</v>
+      <c r="C65" s="21" t="n">
+        <v>89102.6615</v>
+      </c>
+      <c r="D65" s="21" t="n">
+        <v>110233.3576</v>
+      </c>
+      <c r="E65" s="21" t="n">
+        <v>132720.9626</v>
+      </c>
+      <c r="F65" s="21" t="n">
+        <v>156922.6301</v>
+      </c>
+      <c r="G65" s="21" t="n">
+        <v>183018.8635</v>
+      </c>
+      <c r="H65" s="21" t="n">
+        <v>210517.4478</v>
+      </c>
+      <c r="I65" s="21" t="n">
+        <v>238768.8893</v>
+      </c>
+      <c r="J65" s="21" t="n">
+        <v>266979.4335</v>
+      </c>
+      <c r="K65" s="21" t="n">
+        <v>294238.0337</v>
+      </c>
+      <c r="L65" s="21" t="n">
+        <v>319557.2165</v>
+      </c>
+      <c r="M65" s="21" t="n">
+        <v>341926.2217</v>
+      </c>
+      <c r="N65" s="21" t="n">
+        <v>365861.0572</v>
+      </c>
+      <c r="O65" s="21" t="n">
+        <v>391471.3312</v>
+      </c>
+      <c r="P65" s="21" t="n">
+        <v>418874.3244</v>
       </c>
     </row>
     <row r="66">
@@ -1833,6 +3313,36 @@
         <v>1.7231</v>
       </c>
       <c r="F66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="O66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="P66" s="7" t="n">
         <v>1.7231</v>
       </c>
     </row>
@@ -1862,10 +3372,10 @@
           <t>Collection period, days</t>
         </is>
       </c>
-      <c r="B70" s="20" t="n">
+      <c r="B70" s="21" t="n">
         <v>1044.5731</v>
       </c>
-      <c r="C70" s="20" t="n">
+      <c r="C70" s="21" t="n">
         <v>1034.7657</v>
       </c>
     </row>
@@ -1875,10 +3385,10 @@
           <t>Work in progress, days of cost</t>
         </is>
       </c>
-      <c r="B71" s="20" t="n">
+      <c r="B71" s="21" t="n">
         <v>303.6796</v>
       </c>
-      <c r="C71" s="20" t="n">
+      <c r="C71" s="21" t="n">
         <v>270.3102</v>
       </c>
     </row>
@@ -1888,10 +3398,10 @@
           <t>Suppliers, days of cost</t>
         </is>
       </c>
-      <c r="B72" s="20" t="n">
+      <c r="B72" s="21" t="n">
         <v>65.7968</v>
       </c>
-      <c r="C72" s="20" t="n">
+      <c r="C72" s="21" t="n">
         <v>70.12009999999999</v>
       </c>
     </row>
@@ -1914,10 +3424,10 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B74" s="20" t="n">
+      <c r="B74" s="21" t="n">
         <v>62323.5</v>
       </c>
-      <c r="C74" s="20" t="n">
+      <c r="C74" s="21" t="n">
         <v>42238.8</v>
       </c>
     </row>
@@ -1945,7 +3455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1954,6 +3464,16 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1998,6 +3518,36 @@
       <c r="F5" s="19" t="n">
         <v>2030</v>
       </c>
+      <c r="G5" s="19" t="n">
+        <v>2031</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>2033</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>2035</v>
+      </c>
+      <c r="L5" s="19" t="n">
+        <v>2036</v>
+      </c>
+      <c r="M5" s="19" t="n">
+        <v>2037</v>
+      </c>
+      <c r="N5" s="19" t="n">
+        <v>2038</v>
+      </c>
+      <c r="O5" s="19" t="n">
+        <v>2039</v>
+      </c>
+      <c r="P5" s="19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2005,20 +3555,50 @@
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="21" t="n">
         <v>3549.278</v>
       </c>
-      <c r="C6" s="20" t="n">
-        <v>6251.2292</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>10141.4984</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>15742.708</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>23807.3296</v>
+      <c r="C6" s="21" t="n">
+        <v>5318.6321</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>7195.1869</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>9192.2448</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>11341.5235</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>13659.0531</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>16101.1212</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>18610.0485</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>21115.3437</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>23536.0996</v>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>25784.6216</v>
+      </c>
+      <c r="M6" s="21" t="n">
+        <v>27771.1469</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>29896.7291</v>
+      </c>
+      <c r="O6" s="21" t="n">
+        <v>32171.102</v>
+      </c>
+      <c r="P6" s="21" t="n">
+        <v>34604.681</v>
       </c>
     </row>
     <row r="7">
@@ -2027,20 +3607,50 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="n">
         <v>392.607</v>
       </c>
-      <c r="C7" s="20" t="n">
-        <v>565.2756000000001</v>
-      </c>
-      <c r="D7" s="20" t="n">
-        <v>813.8837</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>1171.8298</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>1687.2006</v>
+      <c r="C7" s="21" t="n">
+        <v>505.6778</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>625.5993</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>753.2216</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>890.5715</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>1038.6736</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>1194.7343</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>1355.0676</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>1515.1688</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>1669.8676</v>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>1813.5597</v>
+      </c>
+      <c r="M7" s="21" t="n">
+        <v>1940.5089</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>2076.3445</v>
+      </c>
+      <c r="O7" s="21" t="n">
+        <v>2221.6886</v>
+      </c>
+      <c r="P7" s="21" t="n">
+        <v>2377.2068</v>
       </c>
     </row>
     <row r="8">
@@ -2049,20 +3659,50 @@
           <t>Change in working capital, cash effect</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <v>-443.53</v>
       </c>
-      <c r="C8" s="20" t="n">
-        <v>-1779.5732</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>-3703.2081</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>-6472.8577</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <v>-10460.5991</v>
+      <c r="C8" s="21" t="n">
+        <v>-1318.4287</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>-2246.3353</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>-3233.8274</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>-4296.5887</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>-5442.5456</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>-6650.0835</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>-7890.6814</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>-9129.4835</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>-10326.483</v>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>-11438.3175</v>
+      </c>
+      <c r="M8" s="21" t="n">
+        <v>-12420.6016</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>-13471.6456</v>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>-14596.2626</v>
+      </c>
+      <c r="P8" s="21" t="n">
+        <v>-15799.6029</v>
       </c>
     </row>
     <row r="9">
@@ -2071,20 +3711,50 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="22" t="n">
         <v>3498.355</v>
       </c>
-      <c r="C9" s="21" t="n">
-        <v>5036.9315</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>7252.174</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>10441.6802</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>15033.9311</v>
+      <c r="C9" s="22" t="n">
+        <v>4505.8812</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>5574.451</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>6711.639</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>7935.5064</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>9255.1811</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>10645.772</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <v>12074.4346</v>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>13501.0291</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>14879.4841</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <v>16159.8638</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>17291.0542</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>18501.428</v>
+      </c>
+      <c r="O9" s="22" t="n">
+        <v>19796.528</v>
+      </c>
+      <c r="P9" s="22" t="n">
+        <v>21182.2849</v>
       </c>
     </row>
     <row r="10">
@@ -2108,6 +3778,36 @@
       <c r="F10" s="17" t="n">
         <v>0.0871</v>
       </c>
+      <c r="G10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2115,20 +3815,50 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>-401.4792</v>
       </c>
-      <c r="C11" s="20" t="n">
-        <v>-578.0498</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>-832.2761</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>-1198.3111</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>-1725.3284</v>
+      <c r="C11" s="21" t="n">
+        <v>-517.1052</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>-639.7368</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-770.2431</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-910.6969</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>-1062.1458</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>-1221.7332</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>-1385.6898</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>-1549.409</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>-1707.6037</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>-1854.543</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>-1984.361</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>-2123.2662</v>
+      </c>
+      <c r="O11" s="21" t="n">
+        <v>-2271.8949</v>
+      </c>
+      <c r="P11" s="21" t="n">
+        <v>-2430.9275</v>
       </c>
     </row>
     <row r="12">
@@ -2137,19 +3867,49 @@
           <t>New borrowing drawn</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2159,19 +3919,49 @@
           <t>Cash from financing</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2181,20 +3971,50 @@
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="22" t="n">
         <v>12516.3758</v>
       </c>
-      <c r="C14" s="21" t="n">
-        <v>16975.2575</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>23395.1555</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>32638.5245</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>45947.1273</v>
+      <c r="C14" s="22" t="n">
+        <v>16505.1518</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>21439.866</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>27381.2619</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>34406.0714</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>42599.1067</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>52023.1456</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <v>62711.8904</v>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>74663.5105</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>87835.391</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <v>102140.7118</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <v>117447.405</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>133825.5668</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>151350.1999</v>
+      </c>
+      <c r="P14" s="22" t="n">
+        <v>170101.5573</v>
       </c>
     </row>
     <row r="15">
@@ -2203,19 +4023,49 @@
           <t>Cumulative new borrowing</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2247,6 +4097,36 @@
       <c r="F18" s="19" t="n">
         <v>2030</v>
       </c>
+      <c r="G18" s="19" t="n">
+        <v>2031</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>2033</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>2035</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v>2036</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>2037</v>
+      </c>
+      <c r="N18" s="19" t="n">
+        <v>2038</v>
+      </c>
+      <c r="O18" s="19" t="n">
+        <v>2039</v>
+      </c>
+      <c r="P18" s="19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2254,20 +4134,50 @@
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="21" t="n">
         <v>3549.278</v>
       </c>
-      <c r="C19" s="20" t="n">
-        <v>6251.2292</v>
-      </c>
-      <c r="D19" s="20" t="n">
-        <v>10141.4984</v>
-      </c>
-      <c r="E19" s="20" t="n">
-        <v>15742.708</v>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>23807.3296</v>
+      <c r="C19" s="21" t="n">
+        <v>5318.6321</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>7195.1869</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>9192.2448</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>11341.5235</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>13659.0531</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>16101.1212</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>18610.0485</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>21115.3437</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>23536.0996</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>25784.6216</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>27771.1469</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>29896.7291</v>
+      </c>
+      <c r="O19" s="21" t="n">
+        <v>32171.102</v>
+      </c>
+      <c r="P19" s="21" t="n">
+        <v>34604.681</v>
       </c>
     </row>
     <row r="20">
@@ -2276,20 +4186,50 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="21" t="n">
         <v>392.607</v>
       </c>
-      <c r="C20" s="20" t="n">
-        <v>565.2756000000001</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>813.8837</v>
-      </c>
-      <c r="E20" s="20" t="n">
-        <v>1171.8298</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>1687.2006</v>
+      <c r="C20" s="21" t="n">
+        <v>505.6778</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>625.5993</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>753.2216</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>890.5715</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>1038.6736</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>1194.7343</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>1355.0676</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>1515.1688</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <v>1669.8676</v>
+      </c>
+      <c r="L20" s="21" t="n">
+        <v>1813.5597</v>
+      </c>
+      <c r="M20" s="21" t="n">
+        <v>1940.5089</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>2076.3445</v>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>2221.6886</v>
+      </c>
+      <c r="P20" s="21" t="n">
+        <v>2377.2068</v>
       </c>
     </row>
     <row r="21">
@@ -2298,20 +4238,50 @@
           <t>Change in working capital, cash effect</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="21" t="n">
         <v>-6855.585</v>
       </c>
-      <c r="C21" s="20" t="n">
-        <v>-30424.9616</v>
-      </c>
-      <c r="D21" s="20" t="n">
-        <v>-43805.8597</v>
-      </c>
-      <c r="E21" s="20" t="n">
-        <v>-63071.6768</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>-90810.6002</v>
+      <c r="C21" s="21" t="n">
+        <v>-19923.5765</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>-21130.6962</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>-22487.605</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>-24201.6675</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>-26096.2334</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <v>-27498.5842</v>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>-28251.4415</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <v>-28210.5443</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <v>-27258.6002</v>
+      </c>
+      <c r="L21" s="21" t="n">
+        <v>-25319.1828</v>
+      </c>
+      <c r="M21" s="21" t="n">
+        <v>-22369.0052</v>
+      </c>
+      <c r="N21" s="21" t="n">
+        <v>-23934.8355</v>
+      </c>
+      <c r="O21" s="21" t="n">
+        <v>-25610.274</v>
+      </c>
+      <c r="P21" s="21" t="n">
+        <v>-27402.9932</v>
       </c>
     </row>
     <row r="22">
@@ -2320,20 +4290,50 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="22" t="n">
         <v>-2913.7</v>
       </c>
-      <c r="C22" s="21" t="n">
-        <v>-23608.4569</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>-32850.4776</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>-46157.139</v>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>-65316.07</v>
+      <c r="C22" s="22" t="n">
+        <v>-14099.2666</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>-13309.9099</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>-12542.1386</v>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>-11969.5725</v>
+      </c>
+      <c r="G22" s="22" t="n">
+        <v>-11398.5068</v>
+      </c>
+      <c r="H22" s="22" t="n">
+        <v>-10202.7287</v>
+      </c>
+      <c r="I22" s="22" t="n">
+        <v>-8286.3254</v>
+      </c>
+      <c r="J22" s="22" t="n">
+        <v>-5580.0317</v>
+      </c>
+      <c r="K22" s="22" t="n">
+        <v>-2052.633</v>
+      </c>
+      <c r="L22" s="22" t="n">
+        <v>2278.9985</v>
+      </c>
+      <c r="M22" s="22" t="n">
+        <v>7342.6507</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>8038.2381</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>8782.516600000001</v>
+      </c>
+      <c r="P22" s="22" t="n">
+        <v>9578.894700000001</v>
       </c>
     </row>
     <row r="23">
@@ -2346,16 +4346,46 @@
         <v>-0.0726</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>-0.4084</v>
+        <v>-0.2727</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>-0.3947</v>
+        <v>-0.2081</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.3852</v>
+        <v>-0.1628</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>-0.3786</v>
+        <v>-0.1314</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>-0.1073</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>-0.0835</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>-0.0598</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="N23" s="17" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>0.0394</v>
       </c>
     </row>
     <row r="24">
@@ -2364,20 +4394,50 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="21" t="n">
         <v>-401.4792</v>
       </c>
-      <c r="C24" s="20" t="n">
-        <v>-578.0498</v>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>-832.2761</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>-1198.3111</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>-1725.3284</v>
+      <c r="C24" s="21" t="n">
+        <v>-517.1052</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>-639.7368</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>-770.2431</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>-910.6969</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>-1062.1458</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>-1221.7332</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>-1385.6898</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>-1549.409</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>-1707.6037</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>-1854.543</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>-1984.361</v>
+      </c>
+      <c r="N24" s="21" t="n">
+        <v>-2123.2662</v>
+      </c>
+      <c r="O24" s="21" t="n">
+        <v>-2271.8949</v>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>-2430.9275</v>
       </c>
     </row>
     <row r="25">
@@ -2386,20 +4446,50 @@
           <t>New borrowing drawn</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="20" t="n">
-        <v>20437.0609</v>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>33682.7537</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>47355.4501</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>67041.39840000001</v>
+      <c r="C25" s="21" t="n">
+        <v>10866.926</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>13949.6467</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>13312.3816</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>12880.2694</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>12460.6525</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>11424.4619</v>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>9672.0152</v>
+      </c>
+      <c r="J25" s="21" t="n">
+        <v>7129.4407</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <v>3760.2366</v>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2408,20 +4498,50 @@
           <t>Cash from financing</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="20" t="n">
-        <v>20437.0609</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>33682.7537</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <v>47355.4501</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>67041.39840000001</v>
+      <c r="C26" s="21" t="n">
+        <v>10866.926</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>13949.6467</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>13312.3816</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>12880.2694</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>12460.6525</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>11424.4619</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>9672.0152</v>
+      </c>
+      <c r="J26" s="21" t="n">
+        <v>7129.4407</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>3760.2366</v>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2430,20 +4550,50 @@
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="22" t="n">
         <v>6104.3208</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="22" t="n">
         <v>2354.875</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="22" t="n">
         <v>2354.875</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="22" t="n">
         <v>2354.875</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="22" t="n">
         <v>2354.875</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="H27" s="22" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="J27" s="22" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="K27" s="22" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="L27" s="22" t="n">
+        <v>2779.3305</v>
+      </c>
+      <c r="M27" s="22" t="n">
+        <v>8137.6202</v>
+      </c>
+      <c r="N27" s="22" t="n">
+        <v>14052.592</v>
+      </c>
+      <c r="O27" s="22" t="n">
+        <v>20563.2138</v>
+      </c>
+      <c r="P27" s="22" t="n">
+        <v>27711.1809</v>
       </c>
     </row>
     <row r="28">
@@ -2452,20 +4602,50 @@
           <t>Cumulative new borrowing</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="20" t="n">
-        <v>20437.0609</v>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>54119.8145</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>101475.2646</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>168516.663</v>
+      <c r="C28" s="21" t="n">
+        <v>10866.926</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>24816.5727</v>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>38128.9543</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>51009.2237</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>63469.8762</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>74894.33809999999</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>84566.3533</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <v>91695.79399999999</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>95456.0307</v>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>95456.0307</v>
+      </c>
+      <c r="M28" s="21" t="n">
+        <v>95456.0307</v>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>95456.0307</v>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>95456.0307</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>95456.0307</v>
       </c>
     </row>
     <row r="30">
@@ -2481,7 +4661,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="28" t="n">
         <v>0.043334</v>
       </c>
     </row>
@@ -2491,7 +4671,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="B32" s="27" t="n">
+      <c r="B32" s="28" t="n">
         <v>0.1787</v>
       </c>
     </row>
@@ -2501,7 +4681,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="28" t="n">
         <v>0.039376</v>
       </c>
     </row>
@@ -2511,7 +4691,7 @@
           <t xml:space="preserve">  mean, carried above</t>
         </is>
       </c>
-      <c r="B34" s="27" t="n">
+      <c r="B34" s="28" t="n">
         <v>0.08713700000000001</v>
       </c>
     </row>
@@ -2922,120 +5102,120 @@
           <t>Cash conversion</t>
         </is>
       </c>
-      <c r="B4" s="28" t="n">
-        <v>0.2225000851091698</v>
-      </c>
-      <c r="C4" s="28" t="n">
-        <v>0.2425000851091698</v>
-      </c>
-      <c r="D4" s="28" t="n">
-        <v>0.2625000851091698</v>
-      </c>
-      <c r="E4" s="28" t="n">
-        <v>0.2825000851091698</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>0.3025000851091698</v>
+      <c r="B4" s="29" t="n">
+        <v>0.2225000851091697</v>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>0.2425000851091697</v>
+      </c>
+      <c r="D4" s="29" t="n">
+        <v>0.2625000851091697</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>0.2825000851091697</v>
+      </c>
+      <c r="F4" s="29" t="n">
+        <v>0.3025000851091697</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n">
+      <c r="A5" s="20" t="n">
         <v>0.03937593483976742</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>8.85</v>
+        <v>14.45</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6.29</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>4.46</v>
+        <v>5.8</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3.08</v>
+        <v>3.76</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="20" t="n">
         <v>0.06</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>15.2</v>
+        <v>23.63</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>11.47</v>
+        <v>15.39</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>8.81</v>
+        <v>10.7</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>6.81</v>
+        <v>7.68</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5.26</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="20" t="n">
         <v>0.08713663734609707</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>23.56</v>
+        <v>35.71</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>18.3</v>
+        <v>23.86</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>14.54</v>
+        <v>17.15</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>11.72</v>
+        <v>12.84</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>9.539999999999999</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="20" t="n">
         <v>0.12</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>33.68</v>
+        <v>50.33</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>26.56</v>
+        <v>34.12</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>21.47</v>
+        <v>24.96</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>17.66</v>
+        <v>19.09</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>14.71</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="20" t="n">
         <v>0.1787001284632628</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>51.77</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>41.32</v>
+        <v>52.45</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>33.86</v>
+        <v>38.91</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>28.28</v>
+        <v>30.26</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>23.96</v>
+        <v>24.26</v>
       </c>
     </row>
   </sheetData>
@@ -3241,16 +5421,16 @@
       <c r="C5" s="31" t="n">
         <v>1.4718</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="26" t="n">
         <v>0.3261</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>0.1848</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="26" t="n">
         <v>0.4394</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="26" t="n">
         <v>-0.4419</v>
       </c>
     </row>
@@ -3268,16 +5448,16 @@
       <c r="C6" s="31" t="n">
         <v>1.0493</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <v>0.2988</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>0.1823</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <v>0.4391</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <v>-0.4866</v>
       </c>
     </row>
@@ -3295,16 +5475,16 @@
       <c r="C7" s="31" t="n">
         <v>0.8837</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <v>0.321</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>0.173</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <v>0.4636</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <v>-0.4293</v>
       </c>
     </row>
@@ -3322,16 +5502,16 @@
       <c r="C8" s="31" t="n">
         <v>0.7653</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <v>0.2884</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>0.1815</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>0.444</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="26" t="n">
         <v>-0.3958</v>
       </c>
     </row>
@@ -3349,16 +5529,16 @@
       <c r="C9" s="31" t="n">
         <v>0.7388</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <v>0.2441</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>0.1692</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <v>0.4106</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <v>-0.4712</v>
       </c>
     </row>
@@ -3376,16 +5556,16 @@
       <c r="C10" s="31" t="n">
         <v>0.7067</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <v>0.2576</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>0.1864</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>0.4217</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="26" t="n">
         <v>-0.5199</v>
       </c>
     </row>
@@ -3403,16 +5583,16 @@
       <c r="C11" s="31" t="n">
         <v>0.4938</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <v>0.1033</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>0.2237</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <v>0.4713</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <v>-0.4658</v>
       </c>
     </row>
@@ -3434,7 +5614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3492,244 +5672,219 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>3.08</v>
+        <v>3.76</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>14.54</v>
+        <v>17.15</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0.45</v>
-      </c>
+        <v>44.85</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Book value of equity</t>
+          <t>Earnings multiple on own history</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5.97</v>
+        <v>7.45</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>6.63</v>
+        <v>11.17</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>0.15</v>
-      </c>
+        <v>17.37</v>
+      </c>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Earnings multiple on own history</t>
+          <t>Book value of equity — a disclosed floor</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>7.45</v>
+        <v>5.97</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>11.17</v>
+        <v>6.63</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>17.37</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>0.2</v>
-      </c>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Normalised earnings power</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Weighted central</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7.26</v>
+        <v>3.76</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>8.390000000000001</v>
+        <v>17.15</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>9.94</v>
+        <v>44.85</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>23.54</v>
-      </c>
-      <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Equity (EGP mn)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Valuation</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Equity (EGP mn)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Weak cash conversion (3.9%)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>16588</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>35789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Weak cash conversion (3.9%)</t>
+          <t>Average cash conversion (8.7%)</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>4.46</v>
+        <v>17.15</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>12747</v>
+        <v>49052</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>31759</v>
+        <v>69848</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Average cash conversion (8.7%)</t>
+          <t>Strong cash conversion (17.9%)</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>14.54</v>
+        <v>38.91</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>41571</v>
+        <v>111291</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>61999</v>
+        <v>135145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Strong cash conversion (17.9%)</t>
+          <t>Average, alternative country-risk basis</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>33.86</v>
+        <v>17.54</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>96831</v>
+        <v>50172</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>119975</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Average, alternative country-risk basis</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>46600</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>67276</v>
+        <v>71023</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Market price, 23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>15.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Market price, 23 Aug 2026</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>15.2</v>
+          <t>Book value of equity per share</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>6.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Book value of equity per share</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
           <t>Cash conversion implied by the market price</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>0.09030000000000001</v>
+      <c r="B18" s="9" t="n">
+        <v>0.0789</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Weighted average, rating basis</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>0.2625000851091698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Weighted average, rating basis</t>
+          <t>Weighted average, swap basis</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.2625000851091698</v>
+        <v>0.2523786184712106</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Weighted average, swap basis</t>
+          <t>11 June 2026 edition used</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>0.2523786184712106</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>11 June 2026 edition used</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -3772,7 +5927,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>23030.2</v>
+        <v>48338.4</v>
       </c>
     </row>
     <row r="5">
@@ -3782,7 +5937,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>38969.3</v>
+        <v>21510</v>
       </c>
     </row>
     <row r="6">
@@ -4177,7 +6332,7 @@
         </is>
       </c>
       <c r="B20" s="14" t="n">
-        <v>1885.549516413187</v>
+        <v>2035.093098749406</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -4207,7 +6362,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>21.2924257096</v>
+        <v>19.727806568</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -4348,7 +6503,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>61999.5</v>
+        <v>69848.39999999999</v>
       </c>
     </row>
     <row r="5">
@@ -5058,7 +7213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5067,6 +7222,16 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5104,328 +7269,954 @@
       <c r="F4" s="19" t="n">
         <v>2030</v>
       </c>
+      <c r="G4" s="19" t="n">
+        <v>2031</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>2033</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>2035</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>2036</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>2037</v>
+      </c>
+      <c r="N4" s="19" t="n">
+        <v>2038</v>
+      </c>
+      <c r="O4" s="19" t="n">
+        <v>2039</v>
+      </c>
+      <c r="P4" s="19" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Units delivered</t>
-        </is>
-      </c>
-      <c r="B5" s="20">
-        <f>Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="C5" s="20">
-        <f>B5*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="D5" s="20">
-        <f>C5*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="E5" s="20">
-        <f>D5*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="F5" s="20">
-        <f>E5*(1+Assumptions!$B$21)</f>
-        <v/>
+          <t>Price and cost escalation</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P5" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>the house inflation path</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Revenue per delivered unit</t>
-        </is>
-      </c>
-      <c r="B6" s="7">
-        <f>Assumptions!$B$22</f>
-        <v/>
-      </c>
-      <c r="C6" s="7">
-        <f>B6*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="D6" s="7">
-        <f>C6*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="E6" s="7">
-        <f>D6*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="F6" s="7">
-        <f>E6*(1+Assumptions!$B$10)</f>
-        <v/>
+          <t>Growth in units delivered</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L6" s="20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="M6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>the disclosed run, fading to nothing</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Units delivered</t>
         </is>
       </c>
       <c r="B7" s="21">
-        <f>B5*B6</f>
+        <f>Assumptions!$B$20</f>
         <v/>
       </c>
       <c r="C7" s="21">
-        <f>C5*C6</f>
+        <f>B7*(1+C6)</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>D5*D6</f>
+        <f>C7*(1+D6)</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>E5*E6</f>
+        <f>D7*(1+E6)</f>
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>F5*F6</f>
+        <f>E7*(1+F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>F7*(1+G6)</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>G7*(1+H6)</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>H7*(1+I6)</f>
+        <v/>
+      </c>
+      <c r="J7" s="21">
+        <f>I7*(1+J6)</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>J7*(1+K6)</f>
+        <v/>
+      </c>
+      <c r="L7" s="21">
+        <f>K7*(1+L6)</f>
+        <v/>
+      </c>
+      <c r="M7" s="21">
+        <f>L7*(1+M6)</f>
+        <v/>
+      </c>
+      <c r="N7" s="21">
+        <f>M7*(1+N6)</f>
+        <v/>
+      </c>
+      <c r="O7" s="21">
+        <f>N7*(1+O6)</f>
+        <v/>
+      </c>
+      <c r="P7" s="21">
+        <f>O7*(1+P6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>B7*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="C8" s="20">
-        <f>C7*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="D8" s="20">
-        <f>D7*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="E8" s="20">
-        <f>E7*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="F8" s="20">
-        <f>F7*Assumptions!$B$8</f>
+          <t>Revenue per delivered unit</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="C8" s="7">
+        <f>B8*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D8" s="7">
+        <f>C8*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E8" s="7">
+        <f>D8*(1+E5)</f>
+        <v/>
+      </c>
+      <c r="F8" s="7">
+        <f>E8*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G8" s="7">
+        <f>F8*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H8" s="7">
+        <f>G8*(1+H5)</f>
+        <v/>
+      </c>
+      <c r="I8" s="7">
+        <f>H8*(1+I5)</f>
+        <v/>
+      </c>
+      <c r="J8" s="7">
+        <f>I8*(1+J5)</f>
+        <v/>
+      </c>
+      <c r="K8" s="7">
+        <f>J8*(1+K5)</f>
+        <v/>
+      </c>
+      <c r="L8" s="7">
+        <f>K8*(1+L5)</f>
+        <v/>
+      </c>
+      <c r="M8" s="7">
+        <f>L8*(1+M5)</f>
+        <v/>
+      </c>
+      <c r="N8" s="7">
+        <f>M8*(1+N5)</f>
+        <v/>
+      </c>
+      <c r="O8" s="7">
+        <f>N8*(1+O5)</f>
+        <v/>
+      </c>
+      <c r="P8" s="7">
+        <f>O8*(1+P5)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Overheads</t>
-        </is>
-      </c>
-      <c r="B9" s="20">
-        <f>-B7*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="C9" s="20">
-        <f>-C7*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="D9" s="20">
-        <f>-D7*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="E9" s="20">
-        <f>-E7*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="F9" s="20">
-        <f>-F7*Assumptions!$B$9</f>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="22">
+        <f>B7*B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="22">
+        <f>C7*C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
+        <f>D7*D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>E7*E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="22">
+        <f>F7*F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>G7*G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="22">
+        <f>H7*H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>I7*I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>J7*J8</f>
+        <v/>
+      </c>
+      <c r="K9" s="22">
+        <f>K7*K8</f>
+        <v/>
+      </c>
+      <c r="L9" s="22">
+        <f>L7*L8</f>
+        <v/>
+      </c>
+      <c r="M9" s="22">
+        <f>M7*M8</f>
+        <v/>
+      </c>
+      <c r="N9" s="22">
+        <f>N7*N8</f>
+        <v/>
+      </c>
+      <c r="O9" s="22">
+        <f>O7*O8</f>
+        <v/>
+      </c>
+      <c r="P9" s="22">
+        <f>P7*P8</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Operating cash flow</t>
-        </is>
-      </c>
-      <c r="B10" s="20">
-        <f>B7*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="C10" s="20">
-        <f>C7*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="D10" s="20">
-        <f>D7*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E10" s="20">
-        <f>E7*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="F10" s="20">
-        <f>F7*Assumptions!$B$5</f>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B10" s="21">
+        <f>B9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="C10" s="21">
+        <f>C9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>D9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>E9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>F9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>G9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>H9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="I10" s="21">
+        <f>I9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="J10" s="21">
+        <f>J9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="K10" s="21">
+        <f>K9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="L10" s="21">
+        <f>L9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="M10" s="21">
+        <f>M9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="N10" s="21">
+        <f>N9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="O10" s="21">
+        <f>O9*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="P10" s="21">
+        <f>P9*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure</t>
-        </is>
-      </c>
-      <c r="B11" s="20">
-        <f>-B7*Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="C11" s="20">
-        <f>-C7*Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="D11" s="20">
-        <f>-D7*Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="E11" s="20">
-        <f>-E7*Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="F11" s="20">
-        <f>-F7*Assumptions!$B$23</f>
+          <t>Overheads</t>
+        </is>
+      </c>
+      <c r="B11" s="21">
+        <f>-B9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="C11" s="21">
+        <f>-C9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>-D9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>-E9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>-F9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>-G9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>-H9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>-I9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <f>-J9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>-K9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="L11" s="21">
+        <f>-L9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="M11" s="21">
+        <f>-M9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="N11" s="21">
+        <f>-N9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="O11" s="21">
+        <f>-O9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>-P9*Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>plus finance cost, after tax</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n">
-        <v>2594.3</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>2594.3</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>2594.3</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>2594.3</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>2594.3</v>
+          <t>Operating cash flow</t>
+        </is>
+      </c>
+      <c r="B12" s="21">
+        <f>B9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="C12" s="21">
+        <f>C9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>D9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>E9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>F9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>G9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>H9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="I12" s="21">
+        <f>I9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="J12" s="21">
+        <f>J9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>K9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="L12" s="21">
+        <f>L9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="M12" s="21">
+        <f>M9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="N12" s="21">
+        <f>N9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="O12" s="21">
+        <f>O9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="P12" s="21">
+        <f>P9*Assumptions!$B$5</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Free cash flow to the firm</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Maintenance capital expenditure</t>
         </is>
       </c>
       <c r="B13" s="21">
-        <f>B10+B12+B11</f>
+        <f>-B9*Assumptions!$B$23</f>
         <v/>
       </c>
       <c r="C13" s="21">
-        <f>C10+C12+C11</f>
+        <f>-C9*Assumptions!$B$23</f>
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>D10+D12+D11</f>
+        <f>-D9*Assumptions!$B$23</f>
         <v/>
       </c>
       <c r="E13" s="21">
-        <f>E10+E12+E11</f>
+        <f>-E9*Assumptions!$B$23</f>
         <v/>
       </c>
       <c r="F13" s="21">
-        <f>F10+F12+F11</f>
+        <f>-F9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>-G9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="H13" s="21">
+        <f>-H9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="I13" s="21">
+        <f>-I9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="J13" s="21">
+        <f>-J9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="K13" s="21">
+        <f>-K9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="L13" s="21">
+        <f>-L9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="M13" s="21">
+        <f>-M9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="N13" s="21">
+        <f>-N9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="O13" s="21">
+        <f>-O9*Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="P13" s="21">
+        <f>-P9*Assumptions!$B$23</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="B14" s="22">
-        <f>1/(1+Assumptions!$B$12)^1</f>
-        <v/>
-      </c>
-      <c r="C14" s="22">
-        <f>1/(1+Assumptions!$B$12)^2</f>
-        <v/>
-      </c>
-      <c r="D14" s="22">
-        <f>1/(1+Assumptions!$B$12)^3</f>
-        <v/>
-      </c>
-      <c r="E14" s="22">
-        <f>1/(1+Assumptions!$B$12)^4</f>
-        <v/>
-      </c>
-      <c r="F14" s="22">
-        <f>1/(1+Assumptions!$B$12)^5</f>
-        <v/>
+          <t>plus finance cost, after tax</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>2594.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Present value</t>
-        </is>
-      </c>
-      <c r="B15" s="20">
-        <f>B13*B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="20">
-        <f>C13*C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="20">
-        <f>D13*D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="20">
-        <f>E13*E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="20">
-        <f>F13*F14</f>
-        <v/>
+          <t>Free cash flow to the firm</t>
+        </is>
+      </c>
+      <c r="B15" s="22">
+        <f>B12+B14+B13</f>
+        <v/>
+      </c>
+      <c r="C15" s="22">
+        <f>C12+C14+C13</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>D12+D14+D13</f>
+        <v/>
+      </c>
+      <c r="E15" s="22">
+        <f>E12+E14+E13</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f>F12+F14+F13</f>
+        <v/>
+      </c>
+      <c r="G15" s="22">
+        <f>G12+G14+G13</f>
+        <v/>
+      </c>
+      <c r="H15" s="22">
+        <f>H12+H14+H13</f>
+        <v/>
+      </c>
+      <c r="I15" s="22">
+        <f>I12+I14+I13</f>
+        <v/>
+      </c>
+      <c r="J15" s="22">
+        <f>J12+J14+J13</f>
+        <v/>
+      </c>
+      <c r="K15" s="22">
+        <f>K12+K14+K13</f>
+        <v/>
+      </c>
+      <c r="L15" s="22">
+        <f>L12+L14+L13</f>
+        <v/>
+      </c>
+      <c r="M15" s="22">
+        <f>M12+M14+M13</f>
+        <v/>
+      </c>
+      <c r="N15" s="22">
+        <f>N12+N14+N13</f>
+        <v/>
+      </c>
+      <c r="O15" s="22">
+        <f>O12+O14+O13</f>
+        <v/>
+      </c>
+      <c r="P15" s="22">
+        <f>P12+P14+P13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Cost of capital, that year</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>0.226837</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>0.198306</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0.176908</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="N16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>0.162643</v>
+      </c>
+      <c r="P16" s="12" t="n">
+        <v>0.162643</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Sum of the explicit years</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
         </is>
       </c>
       <c r="B17" s="23">
-        <f>SUM(B15:F15)</f>
+        <f>1/(1+B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="23">
+        <f>B17/(1+C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="23">
+        <f>C17/(1+D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="23">
+        <f>D17/(1+E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="23">
+        <f>E17/(1+F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="23">
+        <f>F17/(1+G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="23">
+        <f>G17/(1+H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="23">
+        <f>H17/(1+I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="23">
+        <f>I17/(1+J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="23">
+        <f>J17/(1+K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="23">
+        <f>K17/(1+L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="23">
+        <f>L17/(1+M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="23">
+        <f>M17/(1+N16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="23">
+        <f>N17/(1+O16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="23">
+        <f>O17/(1+P16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Present value</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>B15*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="21">
+        <f>C15*C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>D15*D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>E15*E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>F15*F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>G15*G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="21">
+        <f>H15*H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="21">
+        <f>I15*I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="21">
+        <f>J15*J17</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>K15*K17</f>
+        <v/>
+      </c>
+      <c r="L18" s="21">
+        <f>L15*L17</f>
+        <v/>
+      </c>
+      <c r="M18" s="21">
+        <f>M15*M17</f>
+        <v/>
+      </c>
+      <c r="N18" s="21">
+        <f>N15*N17</f>
+        <v/>
+      </c>
+      <c r="O18" s="21">
+        <f>O15*O17</f>
+        <v/>
+      </c>
+      <c r="P18" s="21">
+        <f>P15*P17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Sum of the explicit years</t>
+        </is>
+      </c>
+      <c r="B20" s="24">
+        <f>SUM(B18:P18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Terminal value, discounted</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n">
-        <v>38969.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B21" s="24" t="n">
+        <v>21510</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B19" s="23">
-        <f>B17+B18</f>
+      <c r="B22" s="24">
+        <f>B20+B21</f>
         <v/>
       </c>
     </row>
@@ -5440,7 +8231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5486,6 +8277,36 @@
       <c r="F4" s="5" t="n">
         <v>2030</v>
       </c>
+      <c r="G4" s="5" t="n">
+        <v>2031</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2033</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2034</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>2035</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2036</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2037</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>2038</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>2039</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5493,19 +8314,49 @@
           <t>Units sold</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>5632.6667</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="24" t="n">
         <v>5632.6667</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="24" t="n">
         <v>5632.6667</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="24" t="n">
         <v>5632.6667</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="G5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="H5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="I5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="J5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="K5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="L5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="M5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="N5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="O5" s="24" t="n">
+        <v>5632.6667</v>
+      </c>
+      <c r="P5" s="24" t="n">
         <v>5632.6667</v>
       </c>
     </row>
@@ -5515,20 +8366,50 @@
           <t>New sales</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
-        <v>139999.495</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <v>175279.3678</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <v>219449.7685</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>274751.1101</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>343988.3898</v>
+      <c r="B6" s="24" t="n">
+        <v>129711.9922</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>145277.4313</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>158352.4001</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>170228.8301</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>182144.8482</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>194894.9876</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>208537.6367</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>223135.2713</v>
+      </c>
+      <c r="J6" s="24" t="n">
+        <v>238754.7402</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>255467.5721</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>273350.3021</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>292484.8233</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <v>312958.7609</v>
+      </c>
+      <c r="O6" s="24" t="n">
+        <v>334865.8741</v>
+      </c>
+      <c r="P6" s="24" t="n">
+        <v>358306.4853</v>
       </c>
     </row>
     <row r="7">
@@ -5537,20 +8418,50 @@
           <t>Units delivered</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
-        <v>1885.5495</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <v>2168.3819</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>2493.6392</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>2867.6851</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>3297.8379</v>
+      <c r="B7" s="24" t="n">
+        <v>2035.0931</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>2340.3571</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>2656.3053</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>2975.0619</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>3287.4434</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>3583.3133</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>3852.0618</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>4083.1855</v>
+      </c>
+      <c r="J7" s="24" t="n">
+        <v>4266.9289</v>
+      </c>
+      <c r="K7" s="24" t="n">
+        <v>4394.9367</v>
+      </c>
+      <c r="L7" s="24" t="n">
+        <v>4460.8608</v>
+      </c>
+      <c r="M7" s="24" t="n">
+        <v>4460.8608</v>
+      </c>
+      <c r="N7" s="24" t="n">
+        <v>4460.8608</v>
+      </c>
+      <c r="O7" s="24" t="n">
+        <v>4460.8608</v>
+      </c>
+      <c r="P7" s="24" t="n">
+        <v>4460.8608</v>
       </c>
     </row>
     <row r="8">
@@ -5559,20 +8470,50 @@
           <t>Revenue per delivered unit</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
-        <v>21.2924</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <v>26.6581</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>33.376</v>
-      </c>
-      <c r="E8" s="24" t="n">
-        <v>41.7867</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>52.317</v>
+      <c r="B8" s="25" t="n">
+        <v>19.7278</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>22.0951</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>24.0837</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>27.7023</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>29.6414</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>31.7163</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <v>33.9365</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>36.312</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>38.8539</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>41.5737</v>
+      </c>
+      <c r="M8" s="25" t="n">
+        <v>44.4838</v>
+      </c>
+      <c r="N8" s="25" t="n">
+        <v>47.5977</v>
+      </c>
+      <c r="O8" s="25" t="n">
+        <v>50.9295</v>
+      </c>
+      <c r="P8" s="25" t="n">
+        <v>54.4946</v>
       </c>
     </row>
     <row r="9">
@@ -5581,20 +8522,50 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>40147.923</v>
       </c>
-      <c r="C9" s="23" t="n">
-        <v>57804.9795</v>
-      </c>
-      <c r="D9" s="23" t="n">
-        <v>83227.60950000001</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>119831.1122</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>172532.8354</v>
+      <c r="C9" s="24" t="n">
+        <v>51710.5248</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <v>63973.6758</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>77024.30560000001</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>91069.6878</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>106214.5769</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>122173.317</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>138568.9762</v>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>154940.9007</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>170760.3667</v>
+      </c>
+      <c r="L9" s="24" t="n">
+        <v>185454.2962</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>198436.097</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>212326.6238</v>
+      </c>
+      <c r="O9" s="24" t="n">
+        <v>227189.4874</v>
+      </c>
+      <c r="P9" s="24" t="n">
+        <v>243092.7515</v>
       </c>
     </row>
     <row r="10">
@@ -5603,20 +8574,50 @@
           <t>Cost per delivered unit</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
-        <v>13.1327</v>
-      </c>
-      <c r="C10" s="24" t="n">
-        <v>16.4421</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>20.5855</v>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>25.773</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>32.2679</v>
+      <c r="B10" s="25" t="n">
+        <v>12.1676</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>13.6278</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>14.8543</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>15.9683</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>17.0861</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>18.2821</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>19.5619</v>
+      </c>
+      <c r="I10" s="25" t="n">
+        <v>20.9312</v>
+      </c>
+      <c r="J10" s="25" t="n">
+        <v>22.3964</v>
+      </c>
+      <c r="K10" s="25" t="n">
+        <v>23.9642</v>
+      </c>
+      <c r="L10" s="25" t="n">
+        <v>25.6416</v>
+      </c>
+      <c r="M10" s="25" t="n">
+        <v>27.4366</v>
+      </c>
+      <c r="N10" s="25" t="n">
+        <v>29.3571</v>
+      </c>
+      <c r="O10" s="25" t="n">
+        <v>31.4121</v>
+      </c>
+      <c r="P10" s="25" t="n">
+        <v>33.611</v>
       </c>
     </row>
     <row r="11">
@@ -5625,20 +8626,50 @@
           <t>Cost of revenue</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>24762.2864</v>
       </c>
-      <c r="C11" s="23" t="n">
-        <v>35652.74</v>
-      </c>
-      <c r="D11" s="23" t="n">
-        <v>51332.815</v>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>73908.98699999999</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>106414.1595</v>
+      <c r="C11" s="24" t="n">
+        <v>31893.8249</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>39457.4455</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>47506.7643</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>56169.6228</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>65510.6311</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>75353.60340000001</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>85466.057</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>95563.8716</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>105320.9429</v>
+      </c>
+      <c r="L11" s="24" t="n">
+        <v>114383.81</v>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>122390.6767</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>130958.0241</v>
+      </c>
+      <c r="O11" s="24" t="n">
+        <v>140125.0858</v>
+      </c>
+      <c r="P11" s="24" t="n">
+        <v>149933.8418</v>
       </c>
     </row>
     <row r="12">
@@ -5647,20 +8678,50 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>15385.6366</v>
       </c>
-      <c r="C12" s="23" t="n">
-        <v>22152.2396</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>31894.7945</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>45922.1252</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>66118.6758</v>
+      <c r="C12" s="24" t="n">
+        <v>19816.6999</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>24516.2303</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>29517.5413</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>34900.065</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>40703.9458</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>46819.7136</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>53102.9192</v>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>59377.0291</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>65439.4238</v>
+      </c>
+      <c r="L12" s="24" t="n">
+        <v>71070.4862</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>76045.42019999999</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>81368.5996</v>
+      </c>
+      <c r="O12" s="24" t="n">
+        <v>87064.4016</v>
+      </c>
+      <c r="P12" s="24" t="n">
+        <v>93158.9097</v>
       </c>
     </row>
     <row r="13">
@@ -5669,19 +8730,49 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <v>0.3832</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <v>0.3832</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <v>0.3832</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>0.3832</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="H13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="K13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="M13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="N13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="O13" s="26" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="P13" s="26" t="n">
         <v>0.3832</v>
       </c>
     </row>
@@ -5691,20 +8782,50 @@
           <t>Overheads</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>7065.816</v>
       </c>
-      <c r="C14" s="23" t="n">
-        <v>10173.3619</v>
-      </c>
-      <c r="D14" s="23" t="n">
-        <v>14647.6064</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>21089.6237</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>30364.8403</v>
+      <c r="C14" s="24" t="n">
+        <v>9100.771000000001</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>11259.0189</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>13555.8587</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>16027.7695</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>18693.1876</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>21501.839</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>24387.3858</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>27268.7555</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>30052.8954</v>
+      </c>
+      <c r="L14" s="24" t="n">
+        <v>32638.9471</v>
+      </c>
+      <c r="M14" s="24" t="n">
+        <v>34923.6734</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>37368.3305</v>
+      </c>
+      <c r="O14" s="24" t="n">
+        <v>39984.1136</v>
+      </c>
+      <c r="P14" s="24" t="n">
+        <v>42783.0016</v>
       </c>
     </row>
     <row r="15">
@@ -5713,20 +8834,50 @@
           <t>Operating profit</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="24" t="n">
         <v>7927.2136</v>
       </c>
-      <c r="C15" s="23" t="n">
-        <v>11413.6021</v>
-      </c>
-      <c r="D15" s="23" t="n">
-        <v>16433.3044</v>
-      </c>
-      <c r="E15" s="23" t="n">
-        <v>23660.6716</v>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>34066.635</v>
+      <c r="C15" s="24" t="n">
+        <v>10210.2511</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>12631.6122</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>15208.461</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>17981.7239</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>20972.0846</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>24123.1403</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>27360.4657</v>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>30593.1048</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>33716.6608</v>
+      </c>
+      <c r="L15" s="24" t="n">
+        <v>36617.9794</v>
+      </c>
+      <c r="M15" s="24" t="n">
+        <v>39181.238</v>
+      </c>
+      <c r="N15" s="24" t="n">
+        <v>41923.9247</v>
+      </c>
+      <c r="O15" s="24" t="n">
+        <v>44858.5994</v>
+      </c>
+      <c r="P15" s="24" t="n">
+        <v>47998.7013</v>
       </c>
     </row>
     <row r="16">
@@ -5735,19 +8886,49 @@
           <t>Finance cost</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>3347.5</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>3347.5</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>3347.5</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <v>3347.5</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="L16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="M16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="N16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="O16" s="24" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="P16" s="24" t="n">
         <v>3347.5</v>
       </c>
     </row>
@@ -5757,20 +8938,50 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="24" t="n">
         <v>4579.7136</v>
       </c>
-      <c r="C17" s="23" t="n">
-        <v>8066.1021</v>
-      </c>
-      <c r="D17" s="23" t="n">
-        <v>13085.8044</v>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>20313.1716</v>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>30719.135</v>
+      <c r="C17" s="24" t="n">
+        <v>6862.7511</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>9284.1122</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>11860.961</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>14634.2239</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>17624.5846</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>20775.6403</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>24012.9657</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>27245.6048</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>30369.1608</v>
+      </c>
+      <c r="L17" s="24" t="n">
+        <v>33270.4794</v>
+      </c>
+      <c r="M17" s="24" t="n">
+        <v>35833.738</v>
+      </c>
+      <c r="N17" s="24" t="n">
+        <v>38576.4247</v>
+      </c>
+      <c r="O17" s="24" t="n">
+        <v>41511.0994</v>
+      </c>
+      <c r="P17" s="24" t="n">
+        <v>44651.2013</v>
       </c>
     </row>
     <row r="18">
@@ -5779,20 +8990,50 @@
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" s="24" t="n">
         <v>3549.278</v>
       </c>
-      <c r="C18" s="23" t="n">
-        <v>6251.2292</v>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>10141.4984</v>
-      </c>
-      <c r="E18" s="23" t="n">
-        <v>15742.708</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>23807.3296</v>
+      <c r="C18" s="24" t="n">
+        <v>5318.6321</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>7195.1869</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>9192.2448</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>11341.5235</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>13659.0531</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>16101.1212</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>18610.0485</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>21115.3437</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>23536.0996</v>
+      </c>
+      <c r="L18" s="24" t="n">
+        <v>25784.6216</v>
+      </c>
+      <c r="M18" s="24" t="n">
+        <v>27771.1469</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>29896.7291</v>
+      </c>
+      <c r="O18" s="24" t="n">
+        <v>32171.102</v>
+      </c>
+      <c r="P18" s="24" t="n">
+        <v>34604.681</v>
       </c>
     </row>
     <row r="19">
@@ -5801,20 +9042,50 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="25" t="n">
         <v>1.241</v>
       </c>
-      <c r="C19" s="24" t="n">
-        <v>2.1858</v>
-      </c>
-      <c r="D19" s="24" t="n">
-        <v>3.5461</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>5.5046</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>8.3245</v>
+      <c r="C19" s="25" t="n">
+        <v>1.8597</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <v>2.5159</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>3.2142</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>3.9657</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>4.776</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>5.6299</v>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>6.5072</v>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>7.3832</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>8.2296</v>
+      </c>
+      <c r="L19" s="25" t="n">
+        <v>9.0159</v>
+      </c>
+      <c r="M19" s="25" t="n">
+        <v>9.7105</v>
+      </c>
+      <c r="N19" s="25" t="n">
+        <v>10.4537</v>
+      </c>
+      <c r="O19" s="25" t="n">
+        <v>11.249</v>
+      </c>
+      <c r="P19" s="25" t="n">
+        <v>12.0999</v>
       </c>
     </row>
     <row r="20">
@@ -5823,20 +9094,50 @@
           <t>Order book, closing</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n">
-        <v>362851.572</v>
-      </c>
-      <c r="C20" s="23" t="n">
-        <v>480325.9603</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <v>616548.1192</v>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>771468.1171</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <v>942923.6716</v>
+      <c r="B20" s="24" t="n">
+        <v>352564.0692</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>446130.9756</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>540509.6999</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>633714.2243999999</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>724789.3848</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>813469.7955</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>899834.1151000001</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>984400.4102</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>1068214.2497</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>1152921.4551</v>
+      </c>
+      <c r="L20" s="24" t="n">
+        <v>1240817.461</v>
+      </c>
+      <c r="M20" s="24" t="n">
+        <v>1334866.1873</v>
+      </c>
+      <c r="N20" s="24" t="n">
+        <v>1435498.3244</v>
+      </c>
+      <c r="O20" s="24" t="n">
+        <v>1543174.7111</v>
+      </c>
+      <c r="P20" s="24" t="n">
+        <v>1658388.4449</v>
       </c>
     </row>
   </sheetData>
